--- a/data/pack/eu/pollo.xlsx
+++ b/data/pack/eu/pollo.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datos" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fuente y licencia" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Datos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Fuente y licencia" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1042"/>
+  <dimension ref="A1:K1043"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -57744,6 +57744,61 @@
         </is>
       </c>
       <c r="K1042" t="inlineStr">
+        <is>
+          <t>Source: European Commission (Agri-food data portal)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1043">
+      <c r="A1043" t="inlineStr">
+        <is>
+          <t>pollo</t>
+        </is>
+      </c>
+      <c r="B1043" t="inlineStr">
+        <is>
+          <t>Pollo</t>
+        </is>
+      </c>
+      <c r="C1043" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="D1043" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="E1043" t="n">
+        <v>2.3503</v>
+      </c>
+      <c r="F1043" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="G1043" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H1043" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="I1043" t="inlineStr">
+        <is>
+          <t>European Commission — Agri-food Data Portal (DG AGRI)</t>
+        </is>
+      </c>
+      <c r="J1043" t="inlineStr">
+        <is>
+          <t>EU-REUSE-2011-833</t>
+        </is>
+      </c>
+      <c r="K1043" t="inlineStr">
         <is>
           <t>Source: European Commission (Agri-food data portal)</t>
         </is>
@@ -57847,7 +57902,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -57858,7 +57913,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>1041</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="9">
@@ -57953,7 +58008,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
